--- a/docs/files/REPORT_FILTRI/RZV - DALLE CESTE MARLIS.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - DALLE CESTE MARLIS.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>31</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>976</v>
+        <v>1328</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>794</v>
+        <v>1070</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>253</v>
+        <v>378</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
+        <v>192</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>287</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>97</v>
+      </c>
+      <c r="H11" s="12" t="n">
         <v>153</v>
       </c>
-      <c r="F11" s="12" t="n">
-        <v>222</v>
-      </c>
-      <c r="G11" s="12" t="n">
-        <v>81</v>
-      </c>
-      <c r="H11" s="12" t="n">
-        <v>95</v>
-      </c>
       <c r="I11" s="12" t="n">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>227</v>
+        <v>299</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>107</v>
+        <v>142</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>176</v>
+        <v>236</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>89</v>
+        <v>122</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>127</v>
+        <v>166</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,35 +929,35 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>86</v>
+        <v>123</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,31 +1037,31 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>103</v>
+        <v>156</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1091,47 +1091,47 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H16" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="J16" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="K16" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="L16" s="12" t="n">
+        <v>104</v>
+      </c>
+      <c r="M16" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I16" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="J16" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="K16" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="L16" s="12" t="n">
-        <v>70</v>
-      </c>
-      <c r="M16" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>23971</t>
+          <t>03992</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>LONIGO</t>
+          <t>SCHIO</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1145,47 +1145,47 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>05887</t>
+          <t>03853</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>FERRARA</t>
+          <t>VERONA</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1195,35 +1195,35 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>BASSI VALERIA</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1234,12 +1234,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>03992</t>
+          <t>23971</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>SCHIO</t>
+          <t>LONIGO</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1253,31 +1253,31 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1288,12 +1288,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>03906</t>
+          <t>05887</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ARZIGNANO</t>
+          <t>FERRARA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1303,105 +1303,105 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>MARCONI ANDREA</t>
+          <t>BASSI VALERIA</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>32</v>
+        <v>94</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>03851</t>
+          <t>05829</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>VERONA</t>
+          <t>FERRARA</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>BASSI VALERIA</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="J21" s="12" t="n">
         <v>15</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>03853</t>
+          <t>13911</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>VERONA</t>
+          <t>ALBETTONE</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,51 +1411,51 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>CARRARO COSA MIHAI EMILIAN</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J22" s="12" t="n">
         <v>15</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>44</v>
+        <v>84</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>13911</t>
+          <t>03906</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>ALBETTONE</t>
+          <t>ARZIGNANO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,35 +1465,35 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>CARRARO COSA MIHAI EMILIAN</t>
+          <t>MARCONI ANDREA</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1504,54 +1504,54 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>05829</t>
+          <t>03851</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>FERRARA</t>
+          <t>VERONA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>BASSI VALERIA</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1577,47 +1577,47 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>03817</t>
+          <t>03793</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>PESCHIERA DEL GARDA</t>
+          <t>BUSSOLENGO</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1631,47 +1631,47 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>03793</t>
+          <t>03817</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>BUSSOLENGO</t>
+          <t>PESCHIERA DEL GARDA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1685,47 +1685,47 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="G27" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="H27" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H27" s="12" t="n">
+      <c r="I27" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="J27" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="I27" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="J27" s="12" t="n">
+      <c r="K27" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K27" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="L27" s="12" t="n">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>03775</t>
+          <t>03827</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI LUPATOTO</t>
+          <t>SAN BONIFACIO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,35 +1735,35 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>MARCONI ANDREA</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1774,12 +1774,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>03827</t>
+          <t>03775</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>SAN BONIFACIO</t>
+          <t>SAN GIOVANNI LUPATOTO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,51 +1789,51 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>MARCONI ANDREA</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>13850</t>
+          <t>03965</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>ZEVIO</t>
+          <t>THIENE</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1843,35 +1843,35 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>BASSI VALERIA</t>
+          <t>CARRARO COSA MIHAI EMILIAN</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
@@ -1882,12 +1882,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>03965</t>
+          <t>13850</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>THIENE</t>
+          <t>ZEVIO</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1897,35 +1897,35 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>CARRARO COSA MIHAI EMILIAN</t>
+          <t>BASSI VALERIA</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="J31" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K31" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L31" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="M31" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="H31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="J31" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L31" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="M31" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F32" s="12" t="n">
         <v>0</v>
@@ -1967,16 +1967,16 @@
         <v>0</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J32" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>0</v>
@@ -2009,22 +2009,22 @@
         </is>
       </c>
       <c r="E33" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="F33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="H33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>1</v>
@@ -2063,19 +2063,19 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J34" s="12" t="n">
         <v>0</v>
@@ -2084,14 +2084,14 @@
         <v>2</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2174,7 +2174,7 @@
         <v>3</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>0</v>
@@ -2228,7 +2228,7 @@
         <v>0</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G37" s="12" t="n">
         <v>0</v>
@@ -2332,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G39" s="12" t="n">
         <v>0</v>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2386,13 +2386,13 @@
         <v>0</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I40" s="12" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G41" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - DALLE CESTE MARLIS.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - DALLE CESTE MARLIS.xlsx
@@ -535,7 +535,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -845,7 +845,7 @@
         <v>299</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.04013377926421405</v>
+        <v>12</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>166</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.108433734939759</v>
+        <v>18</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>101</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0.7821782178217822</v>
+        <v>79</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>123</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0.02439024390243903</v>
+        <v>3</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>156</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>0.1474358974358974</v>
+        <v>23</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>104</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0.009615384615384616</v>
+        <v>1</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>71</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.2816901408450704</v>
+        <v>20</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>66</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.4696969696969697</v>
+        <v>31</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>83</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.6746987951807228</v>
+        <v>56</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>84</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0.04761904761904762</v>
+        <v>4</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>40</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.775</v>
+        <v>31</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>47</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.5957446808510638</v>
+        <v>28</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>54</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>0.09259259259259259</v>
+        <v>5</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>74</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0.02702702702702703</v>
+        <v>2</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>49</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.5510204081632653</v>
+        <v>27</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>31</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0.3225806451612903</v>
+        <v>10</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>35</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>0.02857142857142857</v>
+        <v>1</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/RZV - DALLE CESTE MARLIS.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - DALLE CESTE MARLIS.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>31</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1328</v>
+        <v>1373</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1070</v>
+        <v>1110</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>378</v>
+        <v>404</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>287</v>
+        <v>314</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>56</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>18</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>12</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>17</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,28 +983,28 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J14" s="12" t="n">
         <v>13</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>3</v>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>39</v>
@@ -1049,7 +1049,7 @@
         <v>7</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J15" s="12" t="n">
         <v>21</v>
@@ -1058,14 +1058,14 @@
         <v>19</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>5</v>
@@ -1103,7 +1103,7 @@
         <v>3</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J16" s="12" t="n">
         <v>14</v>
@@ -1112,7 +1112,7 @@
         <v>17</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>1</v>
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J17" s="12" t="n">
         <v>20</v>
@@ -1166,14 +1166,14 @@
         <v>15</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>20</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1199,35 +1199,35 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>3</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1253,19 +1253,19 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J19" s="12" t="n">
         <v>20</v>
@@ -1274,10 +1274,10 @@
         <v>10</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J20" s="12" t="n">
         <v>7</v>
@@ -1328,64 +1328,64 @@
         <v>7</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>05829</t>
+          <t>03906</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>FERRARA</t>
+          <t>ARZIGNANO</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>BASSI VALERIA</t>
+          <t>MARCONI ANDREA</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="J21" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="K21" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L21" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="J21" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="K21" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L21" s="12" t="n">
-        <v>56</v>
-      </c>
       <c r="M21" s="12" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1396,50 +1396,50 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>13911</t>
+          <t>05829</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>ALBETTONE</t>
+          <t>FERRARA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>CARRARO COSA MIHAI EMILIAN</t>
+          <t>BASSI VALERIA</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="J22" s="12" t="n">
         <v>15</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1450,12 +1450,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>03906</t>
+          <t>13911</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>ARZIGNANO</t>
+          <t>ALBETTONE</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,35 +1465,35 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>MARCONI ANDREA</t>
+          <t>CARRARO COSA MIHAI EMILIAN</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>40</v>
+        <v>93</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1523,35 +1523,35 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>37</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1598,26 +1598,26 @@
         <v>2</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>03793</t>
+          <t>03817</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>BUSSOLENGO</t>
+          <t>PESCHIERA DEL GARDA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1631,47 +1631,47 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="H26" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="J26" s="12" t="n">
         <v>12</v>
-      </c>
-      <c r="I26" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="J26" s="12" t="n">
-        <v>4</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>03817</t>
+          <t>03793</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>PESCHIERA DEL GARDA</t>
+          <t>BUSSOLENGO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1685,35 +1685,35 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>0</v>
@@ -1751,23 +1751,23 @@
         <v>0</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J28" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>27</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>0</v>
@@ -1814,14 +1814,14 @@
         <v>1</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1868,7 @@
         <v>1</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>
@@ -1904,7 +1904,7 @@
         <v>16</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>0</v>
@@ -1922,14 +1922,14 @@
         <v>5</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2174,7 +2174,7 @@
         <v>3</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>0</v>
@@ -2332,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G39" s="12" t="n">
         <v>0</v>
@@ -2386,7 +2386,7 @@
         <v>0</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - DALLE CESTE MARLIS.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - DALLE CESTE MARLIS.xlsx
@@ -525,7 +525,7 @@
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Marcelli Emanuele</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1782,11 +1782,7 @@
           <t>SAN GIOVANNI LUPATOTO</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
+      <c r="C29" s="2" t="inlineStr"/>
       <c r="D29" s="2" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -2268,7 +2264,11 @@
           <t>COPPARO</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
           <t>BASSI VALERIA</t>

--- a/docs/files/REPORT_FILTRI/RZV - DALLE CESTE MARLIS.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - DALLE CESTE MARLIS.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>31</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1373</v>
+        <v>1450</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1110</v>
+        <v>1174</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>404</v>
+        <v>428</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,16 +821,16 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>143</v>
@@ -839,13 +839,13 @@
         <v>50</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>327</v>
+        <v>352</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>12</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>19</v>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>24</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,35 +1037,35 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>39</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>19</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>24</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>5</v>
@@ -1103,23 +1103,23 @@
         <v>3</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>17</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1148,13 +1148,13 @@
         <v>72</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>11</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>56</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1199,31 +1199,31 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1253,31 +1253,31 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>8</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>10</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1307,19 +1307,19 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J20" s="12" t="n">
         <v>7</v>
@@ -1328,14 +1328,14 @@
         <v>7</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1361,35 +1361,35 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>0</v>
@@ -1427,7 +1427,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J22" s="12" t="n">
         <v>15</v>
@@ -1436,7 +1436,7 @@
         <v>9</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>0</v>
@@ -1469,19 +1469,19 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>10</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J23" s="12" t="n">
         <v>15</v>
@@ -1490,7 +1490,7 @@
         <v>15</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>6</v>
@@ -1523,28 +1523,28 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>37</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>30</v>
@@ -1558,12 +1558,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>23964</t>
+          <t>03817</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>SAN VITO DI LEGUZZANO</t>
+          <t>PESCHIERA DEL GARDA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1573,35 +1573,35 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>MARCONI ANDREA</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="F25" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="H25" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I25" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="F25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="H25" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="12" t="n">
-        <v>33</v>
-      </c>
       <c r="J25" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K25" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="L25" s="12" t="n">
+        <v>81</v>
+      </c>
+      <c r="M25" s="12" t="n">
         <v>2</v>
-      </c>
-      <c r="L25" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="M25" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1612,12 +1612,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>03817</t>
+          <t>23964</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>PESCHIERA DEL GARDA</t>
+          <t>SAN VITO DI LEGUZZANO</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1627,35 +1627,35 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>MARCONI ANDREA</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="F26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="H26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="F26" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="G26" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="H26" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="I26" s="12" t="n">
-        <v>31</v>
-      </c>
       <c r="J26" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>77</v>
+        <v>11</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1685,28 +1685,28 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>7</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>5</v>
@@ -1739,19 +1739,19 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="12" t="n">
         <v>29</v>
-      </c>
-      <c r="F28" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="H28" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="12" t="n">
-        <v>27</v>
       </c>
       <c r="J28" s="12" t="n">
         <v>8</v>
@@ -1760,10 +1760,10 @@
         <v>3</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1789,19 +1789,19 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J29" s="12" t="n">
         <v>9</v>
@@ -1810,10 +1810,10 @@
         <v>1</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>0</v>
@@ -1855,7 +1855,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J30" s="12" t="n">
         <v>3</v>
@@ -1864,14 +1864,14 @@
         <v>1</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>0</v>
@@ -1909,16 +1909,16 @@
         <v>0</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J31" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>1</v>
@@ -1972,14 +1972,14 @@
         <v>4</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F34" s="12" t="n">
         <v>0</v>
@@ -2077,7 +2077,7 @@
         <v>0</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L34" s="12" t="n">
         <v>9</v>
@@ -2332,13 +2332,13 @@
         <v>0</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" s="12" t="n">
         <v>0</v>
@@ -2386,7 +2386,7 @@
         <v>0</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G41" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - DALLE CESTE MARLIS.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - DALLE CESTE MARLIS.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>31</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1450</v>
+        <v>1509</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1174</v>
+        <v>1228</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>428</v>
+        <v>445</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,28 +821,28 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
+        <v>211</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>348</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>105</v>
+      </c>
+      <c r="H11" s="12" t="n">
         <v>202</v>
       </c>
-      <c r="F11" s="12" t="n">
-        <v>325</v>
-      </c>
-      <c r="G11" s="12" t="n">
-        <v>102</v>
-      </c>
-      <c r="H11" s="12" t="n">
-        <v>187</v>
-      </c>
       <c r="I11" s="12" t="n">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>60</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>352</v>
+        <v>371</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>14</v>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>264</v>
+        <v>292</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>19</v>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>19</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,19 +1037,19 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>39</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J15" s="12" t="n">
         <v>22</v>
@@ -1058,10 +1058,10 @@
         <v>19</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>5</v>
@@ -1103,16 +1103,16 @@
         <v>3</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>17</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>1</v>
@@ -1148,13 +1148,13 @@
         <v>72</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>11</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>56</v>
@@ -1199,35 +1199,35 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>4</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1253,19 +1253,19 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J19" s="12" t="n">
         <v>22</v>
@@ -1274,10 +1274,10 @@
         <v>10</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1288,12 +1288,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>05887</t>
+          <t>03906</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>FERRARA</t>
+          <t>ARZIGNANO</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1303,35 +1303,35 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>BASSI VALERIA</t>
+          <t>MARCONI ANDREA</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>106</v>
+        <v>49</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1342,12 +1342,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>03906</t>
+          <t>05887</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>ARZIGNANO</t>
+          <t>FERRARA</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,89 +1357,89 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>MARCONI ANDREA</t>
+          <t>BASSI VALERIA</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>46</v>
+        <v>108</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05829</t>
+          <t>13911</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>FERRARA</t>
+          <t>ALBETTONE</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>BASSI VALERIA</t>
+          <t>CARRARO COSA MIHAI EMILIAN</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>66</v>
+        <v>108</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1450,54 +1450,54 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>13911</t>
+          <t>05829</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>ALBETTONE</t>
+          <t>FERRARA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>CARRARO COSA MIHAI EMILIAN</t>
+          <t>BASSI VALERIA</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="J23" s="12" t="n">
         <v>15</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1523,35 +1523,35 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>15</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1577,10 +1577,10 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G25" s="12" t="n">
         <v>14</v>
@@ -1589,23 +1589,23 @@
         <v>3</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>7</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>2</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>0</v>
@@ -1643,16 +1643,16 @@
         <v>0</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>7</v>
@@ -1697,7 +1697,7 @@
         <v>14</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J27" s="12" t="n">
         <v>6</v>
@@ -1706,10 +1706,10 @@
         <v>6</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1760,14 +1760,14 @@
         <v>3</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>28</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1789,22 +1789,22 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>1</v>
@@ -1864,14 +1864,14 @@
         <v>1</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
         <v>20</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
         <v>6</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>1</v>
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F32" s="12" t="n">
         <v>0</v>
@@ -1963,7 +1963,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J32" s="12" t="n">
         <v>3</v>
@@ -1972,7 +1972,7 @@
         <v>4</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>0</v>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2332,13 +2332,13 @@
         <v>0</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I39" s="12" t="n">
         <v>0</v>
@@ -2386,7 +2386,7 @@
         <v>0</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - DALLE CESTE MARLIS.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - DALLE CESTE MARLIS.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>31</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1509</v>
+        <v>1632</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1228</v>
+        <v>1308</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>445</v>
+        <v>471</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>371</v>
+        <v>395</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,35 +929,35 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -983,28 +983,28 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>7</v>
@@ -1018,12 +1018,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>03838</t>
+          <t>03994</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>VERONA</t>
+          <t>SCHIO</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1033,35 +1033,35 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>MARCONI ANDREA</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>184</v>
+        <v>131</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1072,12 +1072,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>03994</t>
+          <t>03838</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>SCHIO</t>
+          <t>VERONA</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1087,35 +1087,35 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>MARCONI ANDREA</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>123</v>
+        <v>203</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1145,35 +1145,35 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G17" s="12" t="n">
         <v>11</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1199,35 +1199,35 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1253,31 +1253,31 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1307,31 +1307,31 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>0</v>
@@ -1373,16 +1373,16 @@
         <v>0</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
@@ -1415,28 +1415,28 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>10</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>16</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>7</v>
@@ -1450,50 +1450,50 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05829</t>
+          <t>03851</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>FERRARA</t>
+          <t>VERONA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>BASSI VALERIA</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1504,54 +1504,54 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>03851</t>
+          <t>05829</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>VERONA</t>
+          <t>FERRARA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>Tino Vincenzo</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>BASSI VALERIA</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>25</v>
@@ -1589,35 +1589,35 @@
         <v>3</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>7</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>2</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>23964</t>
+          <t>03793</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>SAN VITO DI LEGUZZANO</t>
+          <t>BUSSOLENGO</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1627,51 +1627,51 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>MARCONI ANDREA</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>13</v>
+        <v>76</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>03793</t>
+          <t>23964</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>BUSSOLENGO</t>
+          <t>SAN VITO DI LEGUZZANO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1681,39 +1681,39 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>MARCONI ANDREA</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="H27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="F27" s="12" t="n">
-        <v>52</v>
-      </c>
-      <c r="G27" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="H27" s="12" t="n">
+      <c r="J27" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="I27" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="J27" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="K27" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1739,35 +1739,35 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="F28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="J28" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K28" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L28" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="M28" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="F28" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="H28" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="J28" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="K28" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="L28" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="M28" s="12" t="n">
-        <v>28</v>
-      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1789,28 +1789,28 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>13</v>
@@ -1843,19 +1843,19 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="F30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="H30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="12" t="n">
         <v>22</v>
-      </c>
-      <c r="F30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="H30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="12" t="n">
-        <v>21</v>
       </c>
       <c r="J30" s="12" t="n">
         <v>3</v>
@@ -1864,14 +1864,14 @@
         <v>1</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
         <v>20</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
         <v>6</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>1</v>
@@ -1951,28 +1951,28 @@
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>0</v>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2170,7 +2170,7 @@
         <v>3</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>0</v>
@@ -2332,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G39" s="12" t="n">
         <v>0</v>
@@ -2386,13 +2386,13 @@
         <v>0</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I40" s="12" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G41" s="12" t="n">
         <v>0</v>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/RZV - DALLE CESTE MARLIS.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - DALLE CESTE MARLIS.xlsx
@@ -1782,7 +1782,11 @@
           <t>SAN GIOVANNI LUPATOTO</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Abdel</t>
+        </is>
+      </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -2264,11 +2268,7 @@
           <t>COPPARO</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
+      <c r="C38" s="2" t="inlineStr"/>
       <c r="D38" s="2" t="inlineStr">
         <is>
           <t>BASSI VALERIA</t>

--- a/docs/files/REPORT_FILTRI/RZV - DALLE CESTE MARLIS.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - DALLE CESTE MARLIS.xlsx
@@ -525,7 +525,7 @@
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Tino Vincenzo</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Emanuele</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Nadir Abdel</t>
+          <t>Fabio Villa</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -2214,11 +2214,7 @@
           <t>SONA</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
+      <c r="C37" s="2" t="inlineStr"/>
       <c r="D37" s="2" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -2372,11 +2368,7 @@
           <t>VERONA</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
+      <c r="C40" s="2" t="inlineStr"/>
       <c r="D40" s="2" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -2426,11 +2418,7 @@
           <t>VILLAFRANCA DI VERONA</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
+      <c r="C41" s="2" t="inlineStr"/>
       <c r="D41" s="2" t="inlineStr">
         <is>
           <t>TBD</t>

--- a/docs/files/REPORT_FILTRI/RZV - DALLE CESTE MARLIS.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - DALLE CESTE MARLIS.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N41" headerRowCount="1">
-  <autoFilter ref="A10:N41"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N42" headerRowCount="1">
+  <autoFilter ref="A10:N42"/>
   <tableColumns count="14">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:N42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -673,7 +673,7 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B7" s="8" t="n">
         <v>1632</v>
@@ -2457,6 +2457,60 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>23973</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>MUSSOLENTE</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>CARRARO COSA MIHAI EMILIAN</t>
+        </is>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>

--- a/docs/files/REPORT_FILTRI/RZV - DALLE CESTE MARLIS.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - DALLE CESTE MARLIS.xlsx
@@ -209,23 +209,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N42" headerRowCount="1">
-  <autoFilter ref="A10:N42"/>
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O42" headerRowCount="1">
+  <autoFilter ref="A10:O42"/>
+  <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
-    <tableColumn id="3" name="Agente"/>
-    <tableColumn id="4" name="CR"/>
-    <tableColumn id="5" name="Vend 2026"/>
-    <tableColumn id="6" name="Vend 2025"/>
-    <tableColumn id="7" name="Ass 2026"/>
-    <tableColumn id="8" name="Ass 2025"/>
-    <tableColumn id="9" name="Prospect"/>
-    <tableColumn id="10" name="Twin"/>
-    <tableColumn id="11" name="Business"/>
-    <tableColumn id="12" name="Sost anno"/>
-    <tableColumn id="13" name="UP EU"/>
-    <tableColumn id="14" name="Stato"/>
+    <tableColumn id="3" name="Indirizzo"/>
+    <tableColumn id="4" name="Agente"/>
+    <tableColumn id="5" name="CR"/>
+    <tableColumn id="6" name="Vend 2026"/>
+    <tableColumn id="7" name="Vend 2025"/>
+    <tableColumn id="8" name="Ass 2026"/>
+    <tableColumn id="9" name="Ass 2025"/>
+    <tableColumn id="10" name="Prospect"/>
+    <tableColumn id="11" name="Twin"/>
+    <tableColumn id="12" name="Business"/>
+    <tableColumn id="13" name="Sost anno"/>
+    <tableColumn id="14" name="UP EU"/>
+    <tableColumn id="15" name="Stato"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -520,23 +521,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N42"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -558,6 +560,7 @@
       <c r="L1" s="2" t="n"/>
       <c r="M1" s="2" t="n"/>
       <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -574,6 +577,7 @@
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -598,6 +602,7 @@
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -622,6 +627,7 @@
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -638,6 +644,7 @@
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -670,6 +677,7 @@
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -694,6 +702,7 @@
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -710,6 +719,7 @@
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -726,6 +736,7 @@
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -740,60 +751,65 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
+          <t>Indirizzo</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>CR</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Vend 2026</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Vend 2025</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>Ass 2026</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>Ass 2025</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>Twin</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Sost anno</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>UP EU</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
@@ -812,42 +828,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>VIA BOLOGNA 632</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>BASSI VALERIA</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>224</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>361</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="H11" s="12" t="n">
         <v>107</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="I11" s="12" t="n">
         <v>217</v>
       </c>
-      <c r="I11" s="12" t="n">
+      <c r="J11" s="12" t="n">
         <v>159</v>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="K11" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="K11" s="12" t="n">
+      <c r="L11" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="L11" s="12" t="n">
+      <c r="M11" s="12" t="n">
         <v>395</v>
       </c>
-      <c r="M11" s="12" t="n">
+      <c r="N11" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -866,42 +887,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>VIA MONTE ORTIGARA 24</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>MARCONI ANDREA</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>177</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>304</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="H12" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="H12" s="12" t="n">
+      <c r="I12" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="I12" s="12" t="n">
+      <c r="J12" s="12" t="n">
         <v>155</v>
       </c>
-      <c r="J12" s="12" t="n">
+      <c r="K12" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="K12" s="12" t="n">
+      <c r="L12" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="L12" s="12" t="n">
+      <c r="M12" s="12" t="n">
         <v>207</v>
       </c>
-      <c r="M12" s="12" t="n">
+      <c r="N12" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -920,42 +946,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>VIA TRIESTE</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>CARRARO COSA MIHAI EMILIAN</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>136</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>163</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="H13" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="H13" s="12" t="n">
+      <c r="I13" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="I13" s="12" t="n">
+      <c r="J13" s="12" t="n">
         <v>106</v>
       </c>
-      <c r="J13" s="12" t="n">
+      <c r="K13" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="K13" s="12" t="n">
+      <c r="L13" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="L13" s="12" t="n">
+      <c r="M13" s="12" t="n">
         <v>130</v>
       </c>
-      <c r="M13" s="12" t="n">
+      <c r="N13" s="12" t="n">
         <v>98</v>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -974,42 +1005,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>SS 47 VALSUGANA KM.42+600</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>CARRARO COSA MIHAI EMILIAN</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>125</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>171</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="H14" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="H14" s="12" t="n">
+      <c r="I14" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="I14" s="12" t="n">
+      <c r="J14" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="J14" s="12" t="n">
+      <c r="K14" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="K14" s="12" t="n">
+      <c r="L14" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="L14" s="12" t="n">
+      <c r="M14" s="12" t="n">
         <v>155</v>
       </c>
-      <c r="M14" s="12" t="n">
+      <c r="N14" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1028,42 +1064,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>VIALE DELL'INDUSTRIA 140</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>MARCONI ANDREA</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>94</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="H15" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="I15" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I15" s="12" t="n">
+      <c r="J15" s="12" t="n">
         <v>77</v>
-      </c>
-      <c r="J15" s="12" t="n">
-        <v>18</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>18</v>
       </c>
       <c r="L15" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="M15" s="12" t="n">
         <v>131</v>
       </c>
-      <c r="M15" s="12" t="n">
+      <c r="N15" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1082,42 +1123,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>VIALE DEL LAVORO 22</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="H16" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="H16" s="12" t="n">
+      <c r="I16" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I16" s="12" t="n">
+      <c r="J16" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="J16" s="12" t="n">
+      <c r="K16" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="K16" s="12" t="n">
+      <c r="L16" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="L16" s="12" t="n">
+      <c r="M16" s="12" t="n">
         <v>203</v>
       </c>
-      <c r="M16" s="12" t="n">
+      <c r="N16" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1136,42 +1182,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>VIA P.MARASCHIN 50</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>MARCONI ANDREA</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>79</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="G17" s="12" t="n">
         <v>88</v>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="H17" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="H17" s="12" t="n">
+      <c r="I17" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="I17" s="12" t="n">
+      <c r="J17" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="J17" s="12" t="n">
+      <c r="K17" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="K17" s="12" t="n">
+      <c r="L17" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="L17" s="12" t="n">
+      <c r="M17" s="12" t="n">
         <v>96</v>
       </c>
-      <c r="M17" s="12" t="n">
+      <c r="N17" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1190,42 +1241,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>VIA FARINATA DEGLI UBERTI 16</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>78</v>
       </c>
-      <c r="F18" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="H18" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="12" t="n">
         <v>69</v>
       </c>
-      <c r="J18" s="12" t="n">
+      <c r="K18" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="K18" s="12" t="n">
+      <c r="L18" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L18" s="12" t="n">
+      <c r="M18" s="12" t="n">
         <v>81</v>
       </c>
-      <c r="M18" s="12" t="n">
+      <c r="N18" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1244,42 +1300,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>VARIANTE SS 500 SNC</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>MARCONI ANDREA</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>135</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="H19" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="H19" s="12" t="n">
+      <c r="I19" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="I19" s="12" t="n">
+      <c r="J19" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="J19" s="12" t="n">
+      <c r="K19" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="K19" s="12" t="n">
+      <c r="L19" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="L19" s="12" t="n">
+      <c r="M19" s="12" t="n">
         <v>103</v>
       </c>
-      <c r="M19" s="12" t="n">
+      <c r="N19" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1298,42 +1359,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>VIA CHIAMPO 19</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>MARCONI ANDREA</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="F20" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H20" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="J20" s="12" t="n">
+      <c r="K20" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="K20" s="12" t="n">
+      <c r="L20" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="L20" s="12" t="n">
+      <c r="M20" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="M20" s="12" t="n">
+      <c r="N20" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1352,42 +1418,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>VIA MODENA, 236/P</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
           <t>BASSI VALERIA</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="F21" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="H21" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="J21" s="12" t="n">
+      <c r="K21" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="K21" s="12" t="n">
+      <c r="L21" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L21" s="12" t="n">
+      <c r="M21" s="12" t="n">
         <v>112</v>
       </c>
-      <c r="M21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="N21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1406,42 +1477,47 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>VIA FORNACI 10    SS 247</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>CARRARO COSA MIHAI EMILIAN</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="H22" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="H22" s="12" t="n">
+      <c r="I22" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="I22" s="12" t="n">
+      <c r="J22" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="J22" s="12" t="n">
+      <c r="K22" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="K22" s="12" t="n">
+      <c r="L22" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="L22" s="12" t="n">
+      <c r="M22" s="12" t="n">
         <v>110</v>
       </c>
-      <c r="M22" s="12" t="n">
+      <c r="N22" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1460,42 +1536,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>VIA G.MAMELI 160/F</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="G23" s="12" t="n">
+      <c r="H23" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="H23" s="12" t="n">
+      <c r="I23" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="I23" s="12" t="n">
+      <c r="J23" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="J23" s="12" t="n">
+      <c r="K23" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="K23" s="12" t="n">
+      <c r="L23" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L23" s="12" t="n">
+      <c r="M23" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="M23" s="12" t="n">
+      <c r="N23" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1514,42 +1595,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>VIA RAVENNA 78</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>BASSI VALERIA</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="F24" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="F24" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H24" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="J24" s="12" t="n">
+      <c r="K24" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="K24" s="12" t="n">
+      <c r="L24" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="L24" s="12" t="n">
+      <c r="M24" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="M24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="N24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1568,42 +1654,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>VIA VENEZIA 76</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="F25" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="G25" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="G25" s="12" t="n">
+      <c r="H25" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="H25" s="12" t="n">
+      <c r="I25" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I25" s="12" t="n">
+      <c r="J25" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="J25" s="12" t="n">
+      <c r="K25" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="K25" s="12" t="n">
+      <c r="L25" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="L25" s="12" t="n">
+      <c r="M25" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="M25" s="12" t="n">
+      <c r="N25" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1622,42 +1713,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>VIA GARDESANA 25</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="F26" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="G26" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="G26" s="12" t="n">
+      <c r="H26" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="H26" s="12" t="n">
+      <c r="I26" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="I26" s="12" t="n">
+      <c r="J26" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="J26" s="12" t="n">
+      <c r="K26" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K26" s="12" t="n">
+      <c r="L26" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L26" s="12" t="n">
+      <c r="M26" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="M26" s="12" t="n">
+      <c r="N26" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1676,42 +1772,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>VIA MARTIRI DELLA LIBERTA 43</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>MARCONI ANDREA</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="F27" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="F27" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="H27" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="J27" s="12" t="n">
+      <c r="K27" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="K27" s="12" t="n">
+      <c r="L27" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L27" s="12" t="n">
+      <c r="M27" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="M27" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="N27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1730,42 +1831,47 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>LOC. VILLABELLA N. 19 S.S. 11</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>MARCONI ANDREA</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="F28" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="F28" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H28" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="J28" s="12" t="n">
+      <c r="K28" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="K28" s="12" t="n">
+      <c r="L28" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="L28" s="12" t="n">
+      <c r="M28" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="M28" s="12" t="n">
+      <c r="N28" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1784,42 +1890,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>VIA GAROFOLI N. 270</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="F29" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="F29" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="H29" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="J29" s="12" t="n">
+      <c r="K29" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="K29" s="12" t="n">
+      <c r="L29" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L29" s="12" t="n">
+      <c r="M29" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="M29" s="12" t="n">
+      <c r="N29" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1838,42 +1949,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>VIA MARCONI 123/A</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>CARRARO COSA MIHAI EMILIAN</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="F30" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="F30" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H30" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="J30" s="12" t="n">
+      <c r="K30" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K30" s="12" t="n">
+      <c r="L30" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L30" s="12" t="n">
+      <c r="M30" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="M30" s="12" t="n">
+      <c r="N30" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1892,42 +2008,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>S.S.434 TRANSPOLESANA KM.7+400</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
           <t>BASSI VALERIA</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="F31" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="G31" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="G31" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="J31" s="12" t="n">
+      <c r="K31" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="K31" s="12" t="n">
+      <c r="L31" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L31" s="12" t="n">
+      <c r="M31" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="M31" s="12" t="n">
+      <c r="N31" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1946,42 +2067,47 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>VIA POSTUMIA N.  86</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="F32" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="F32" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H32" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="12" t="n">
         <v>14</v>
-      </c>
-      <c r="J32" s="12" t="n">
-        <v>6</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L32" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="M32" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="M32" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="N32" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2000,42 +2126,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>VIALE SAN LAZZARO 106</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
           <t>CARRARO COSA MIHAI EMILIAN</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="F33" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="F33" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H33" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="12" t="n">
         <v>10</v>
-      </c>
-      <c r="J33" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L33" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="M33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
+      <c r="N33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2054,42 +2185,47 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>VIA CAMPAGNOL DI TOMBETTA 6</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="F34" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="F34" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H34" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="J34" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="K34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="L34" s="12" t="n">
+      <c r="M34" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="M34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="N34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2108,20 +2244,22 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>VIA J. DAL VERME 188 189</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
           <t>CARRARO COSA MIHAI EMILIAN</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="F35" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F35" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G35" s="12" t="n">
         <v>0</v>
       </c>
@@ -2129,21 +2267,24 @@
         <v>0</v>
       </c>
       <c r="I35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="J35" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="K35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="M35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="N35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2162,42 +2303,47 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>VIA MUSELLE S.S.434 KM 22+224</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>BASSI VALERIA</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="F36" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="G36" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="G36" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H36" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I36" s="12" t="n">
         <v>2</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L36" s="12" t="n">
+      <c r="M36" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="M36" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="N36" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2214,21 +2360,23 @@
           <t>SONA</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr"/>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>LOCALITA' CIVEL 1</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr"/>
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="G37" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H37" s="12" t="n">
         <v>0</v>
       </c>
@@ -2247,7 +2395,10 @@
       <c r="M37" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="N37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2264,27 +2415,29 @@
           <t>COPPARO</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr"/>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>VIA PRIMICELLO 26</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>BASSI VALERIA</t>
         </is>
       </c>
-      <c r="E38" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G38" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I38" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J38" s="12" t="n">
         <v>0</v>
       </c>
@@ -2297,7 +2450,10 @@
       <c r="M38" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="N38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -2316,29 +2472,31 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>VIA VILLAFRANCA 357</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="G39" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I39" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J39" s="12" t="n">
         <v>0</v>
       </c>
@@ -2346,12 +2504,15 @@
         <v>0</v>
       </c>
       <c r="L39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="M39" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
+      <c r="N39" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2368,27 +2529,29 @@
           <t>VERONA</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr"/>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>VIA MANTOVANA 90</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="G40" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I40" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J40" s="12" t="n">
         <v>0</v>
       </c>
@@ -2401,7 +2564,10 @@
       <c r="M40" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N40" s="2" t="inlineStr">
+      <c r="N40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2418,21 +2584,23 @@
           <t>VILLAFRANCA DI VERONA</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr"/>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>VIA SAN GIOVANI PAGLIA 23</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="G41" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H41" s="12" t="n">
         <v>0</v>
       </c>
@@ -2451,7 +2619,10 @@
       <c r="M41" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N41" s="2" t="inlineStr">
+      <c r="N41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2470,17 +2641,19 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Fabio Villa</t>
+          <t>VIA DANTE ALIGHIERI 8</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
           <t>CARRARO COSA MIHAI EMILIAN</t>
         </is>
       </c>
-      <c r="E42" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="F42" s="12" t="n">
         <v>0</v>
       </c>
@@ -2505,7 +2678,10 @@
       <c r="M42" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N42" s="2" t="inlineStr">
+      <c r="N42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>

--- a/docs/files/REPORT_FILTRI/RZV - DALLE CESTE MARLIS.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - DALLE CESTE MARLIS.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>32</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1632</v>
+        <v>1713</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1308</v>
+        <v>1370</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>471</v>
+        <v>499</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>57</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>395</v>
+        <v>416</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I12" s="12" t="n">
         <v>32</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>84</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>20</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>5</v>
@@ -1090,23 +1090,23 @@
         <v>3</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>18</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>39</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I16" s="12" t="n">
         <v>7</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>22</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1172,17 +1172,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>03992</t>
+          <t>03853</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>SCHIO</t>
+          <t>VERONA</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>VIA P.MARASCHIN 50</t>
+          <t>VIA FARINATA DEGLI UBERTI 16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1192,56 +1192,56 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>MARCONI ANDREA</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>03853</t>
+          <t>03992</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>VERONA</t>
+          <t>SCHIO</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>VIA FARINATA DEGLI UBERTI 16</t>
+          <t>VIA P.MARASCHIN 50</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1251,39 +1251,39 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>MARCONI ANDREA</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1314,31 +1314,31 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>135</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>45</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="L19" s="12" t="n">
         <v>14</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1373,35 +1373,35 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L20" s="12" t="n">
         <v>7</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>0</v>
@@ -1444,23 +1444,23 @@
         <v>0</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>8</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1491,31 +1491,31 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>10</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K22" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="L22" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="L22" s="12" t="n">
-        <v>16</v>
-      </c>
       <c r="M22" s="12" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1550,19 +1550,19 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="G23" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="G23" s="12" t="n">
-        <v>51</v>
-      </c>
       <c r="H23" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>23</v>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1630,14 +1630,14 @@
         <v>10</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1668,13 +1668,13 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I25" s="12" t="n">
         <v>3</v>
@@ -1686,13 +1686,13 @@
         <v>14</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1727,35 +1727,35 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>6</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1786,35 +1786,35 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>2</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1866,14 +1866,14 @@
         <v>5</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I29" s="12" t="n">
         <v>0</v>
@@ -1925,14 +1925,14 @@
         <v>1</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>0</v>
@@ -1975,16 +1975,16 @@
         <v>0</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>3</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>1</v>
@@ -2025,13 +2025,13 @@
         <v>20</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" s="12" t="n">
         <v>15</v>
@@ -2043,7 +2043,7 @@
         <v>6</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>1</v>
@@ -2102,14 +2102,14 @@
         <v>6</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2234,17 +2234,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>03993</t>
+          <t>23973</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>VICENZA</t>
+          <t>MUSSOLENTE</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>VIA J. DAL VERME 188 189</t>
+          <t>VIA DANTE ALIGHIERI 47</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2258,28 +2258,28 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N35" s="12" t="n">
         <v>0</v>
@@ -2293,17 +2293,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>13834</t>
+          <t>03993</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>ISOLA RIZZA</t>
+          <t>VICENZA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>VIA MUSELLE S.S.434 KM 22+224</t>
+          <t>VIA J. DAL VERME 188 189</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2313,130 +2313,134 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>BASSI VALERIA</t>
+          <t>CARRARO COSA MIHAI EMILIAN</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
         <v>3</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>03816</t>
+          <t>13834</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>SONA</t>
+          <t>ISOLA RIZZA</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>LOCALITA' CIVEL 1</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr"/>
+          <t>VIA MUSELLE S.S.434 KM 22+224</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>BASSI VALERIA</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>05861</t>
+          <t>03816</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>COPPARO</t>
+          <t>SONA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>VIA PRIMICELLO 26</t>
+          <t>LOCALITA' CIVEL 1</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>BASSI VALERIA</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" s="12" t="n">
         <v>0</v>
@@ -2462,40 +2466,36 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>13862</t>
+          <t>05861</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>VALEGGIO SUL MINCIO</t>
+          <t>COPPARO</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VIA VILLAFRANCA 357</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
+          <t>VIA PRIMICELLO 26</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>BASSI VALERIA</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="H39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J39" s="12" t="n">
         <v>0</v>
@@ -2507,34 +2507,38 @@
         <v>0</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>57208</t>
+          <t>13862</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>VERONA</t>
+          <t>VALEGGIO SUL MINCIO</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>VIA MANTOVANA 90</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr"/>
+          <t>VIA VILLAFRANCA 357</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Fabio Villa</t>
+        </is>
+      </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
           <t>TBD</t>
@@ -2544,13 +2548,13 @@
         <v>0</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J40" s="12" t="n">
         <v>0</v>
@@ -2562,7 +2566,7 @@
         <v>0</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N40" s="12" t="n">
         <v>0</v>
@@ -2576,17 +2580,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>55905</t>
+          <t>57208</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>VILLAFRANCA DI VERONA</t>
+          <t>VERONA</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>VIA SAN GIOVANI PAGLIA 23</t>
+          <t>VIA MANTOVANA 90</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr"/>
@@ -2599,13 +2603,13 @@
         <v>0</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J41" s="12" t="n">
         <v>0</v>
@@ -2624,41 +2628,37 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>23973</t>
+          <t>55905</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>MUSSOLENTE</t>
+          <t>VILLAFRANCA DI VERONA</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>VIA DANTE ALIGHIERI 8</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
+          <t>VIA SAN GIOVANI PAGLIA 23</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>CARRARO COSA MIHAI EMILIAN</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - DALLE CESTE MARLIS.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - DALLE CESTE MARLIS.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>32</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1713</v>
+        <v>1792</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1370</v>
+        <v>1439</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>499</v>
+        <v>532</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,28 +842,28 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>375</v>
+        <v>396</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>416</v>
+        <v>447</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>17</v>
@@ -901,28 +901,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I12" s="12" t="n">
         <v>32</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="L12" s="12" t="n">
         <v>15</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>21</v>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>79</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>28</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>44</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>8</v>
@@ -1078,28 +1078,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>5</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>20</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>1</v>
@@ -1137,52 +1137,52 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>39</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I16" s="12" t="n">
         <v>7</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>22</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>03853</t>
+          <t>03992</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>VERONA</t>
+          <t>SCHIO</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>VIA FARINATA DEGLI UBERTI 16</t>
+          <t>VIA P.MARASCHIN 50</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1192,56 +1192,56 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>MARCONI ANDREA</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="H17" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="I17" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="J17" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="I17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="12" t="n">
-        <v>73</v>
-      </c>
       <c r="K17" s="12" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>03992</t>
+          <t>03853</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>SCHIO</t>
+          <t>VERONA</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>VIA P.MARASCHIN 50</t>
+          <t>VIA FARINATA DEGLI UBERTI 16</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1251,35 +1251,35 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>MARCONI ANDREA</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>107</v>
+        <v>84</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,31 +1314,31 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L19" s="12" t="n">
         <v>14</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1373,22 +1373,22 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L20" s="12" t="n">
         <v>7</v>
@@ -1401,24 +1401,24 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>05887</t>
+          <t>03851</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>FERRARA</t>
+          <t>VERONA</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>VIA MODENA, 236/P</t>
+          <t>VIA G.MAMELI 160/F</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1428,56 +1428,56 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>BASSI VALERIA</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>19</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>113</v>
+        <v>63</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>13911</t>
+          <t>05887</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>ALBETTONE</t>
+          <t>FERRARA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>VIA FORNACI 10    SS 247</t>
+          <t>VIA MODENA, 236/P</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1487,35 +1487,35 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>CARRARO COSA MIHAI EMILIAN</t>
+          <t>BASSI VALERIA</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1526,17 +1526,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>03851</t>
+          <t>13911</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>VERONA</t>
+          <t>ALBETTONE</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VIA G.MAMELI 160/F</t>
+          <t>VIA FORNACI 10    SS 247</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1546,39 +1546,39 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>CARRARO COSA MIHAI EMILIAN</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="H23" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="I23" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="J23" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="K23" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="L23" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="I23" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="J23" s="12" t="n">
-        <v>50</v>
-      </c>
-      <c r="K23" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="L23" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="M23" s="12" t="n">
-        <v>62</v>
+        <v>123</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>0</v>
@@ -1627,17 +1627,17 @@
         <v>16</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1668,35 +1668,35 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G25" s="12" t="n">
         <v>28</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I25" s="12" t="n">
         <v>3</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L25" s="12" t="n">
         <v>11</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>3</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1727,19 +1727,19 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I26" s="12" t="n">
         <v>16</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>6</v>
@@ -1748,7 +1748,7 @@
         <v>12</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>6</v>
@@ -1786,28 +1786,28 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>2</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>0</v>
@@ -1845,35 +1845,35 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L28" s="12" t="n">
         <v>5</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1904,35 +1904,35 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L29" s="12" t="n">
         <v>1</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>14</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>0</v>
@@ -1975,7 +1975,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>3</v>
@@ -1984,14 +1984,14 @@
         <v>2</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2022,10 +2022,10 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>0</v>
@@ -2034,16 +2034,16 @@
         <v>1</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L31" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>1</v>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>6</v>
@@ -2102,14 +2102,14 @@
         <v>6</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
         <v>3</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>0</v>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>0</v>
@@ -2603,13 +2603,13 @@
         <v>0</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J41" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - DALLE CESTE MARLIS.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - DALLE CESTE MARLIS.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>32</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1792</v>
+        <v>1879</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1439</v>
+        <v>1511</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>532</v>
+        <v>564</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,28 +842,28 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>396</v>
+        <v>432</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>237</v>
+        <v>268</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>447</v>
+        <v>470</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>17</v>
@@ -901,28 +901,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>334</v>
+        <v>359</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>69</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>21</v>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>8</v>
@@ -1078,10 +1078,10 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>5</v>
@@ -1090,23 +1090,23 @@
         <v>4</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>39</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I16" s="12" t="n">
         <v>7</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>22</v>
@@ -1158,14 +1158,14 @@
         <v>22</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1196,35 +1196,35 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>13</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>17</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>23</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1261,7 +1261,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>0</v>
@@ -1276,10 +1276,10 @@
         <v>6</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,28 +1314,28 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>28</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>76</v>
@@ -1379,7 +1379,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I20" s="12" t="n">
         <v>0</v>
@@ -1394,14 +1394,14 @@
         <v>7</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1432,52 +1432,52 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L21" s="12" t="n">
         <v>11</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05887</t>
+          <t>13911</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>FERRARA</t>
+          <t>ALBETTONE</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>VIA MODENA, 236/P</t>
+          <t>VIA FORNACI 10    SS 247</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1487,35 +1487,35 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>BASSI VALERIA</t>
+          <t>CARRARO COSA MIHAI EMILIAN</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1526,17 +1526,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>13911</t>
+          <t>05887</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>ALBETTONE</t>
+          <t>FERRARA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VIA FORNACI 10    SS 247</t>
+          <t>VIA MODENA, 236/P</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1546,39 +1546,39 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>CARRARO COSA MIHAI EMILIAN</t>
+          <t>BASSI VALERIA</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>0</v>
@@ -1621,16 +1621,16 @@
         <v>0</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L24" s="12" t="n">
         <v>11</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>0</v>
@@ -1668,35 +1668,35 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>3</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1727,28 +1727,28 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L26" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>6</v>
@@ -1762,17 +1762,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>23964</t>
+          <t>03827</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>SAN VITO DI LEGUZZANO</t>
+          <t>SAN BONIFACIO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>VIA MARTIRI DELLA LIBERTA 43</t>
+          <t>LOC. VILLABELLA N. 19 S.S. 11</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1786,31 +1786,31 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1821,17 +1821,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>03827</t>
+          <t>23964</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>SAN BONIFACIO</t>
+          <t>SAN VITO DI LEGUZZANO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>LOC. VILLABELLA N. 19 S.S. 11</t>
+          <t>VIA MARTIRI DELLA LIBERTA 43</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1845,35 +1845,35 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1904,28 +1904,28 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L29" s="12" t="n">
         <v>1</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>14</v>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>0</v>
@@ -1975,7 +1975,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>3</v>
@@ -1984,7 +1984,7 @@
         <v>2</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>1</v>
@@ -2022,31 +2022,31 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L31" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>0</v>
@@ -2093,16 +2093,16 @@
         <v>0</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L32" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>0</v>
@@ -2258,22 +2258,22 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L35" s="12" t="n">
         <v>0</v>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
         <v>3</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>0</v>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>0</v>
@@ -2603,7 +2603,7 @@
         <v>0</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>0</v>
@@ -2658,7 +2658,7 @@
         <v>0</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - DALLE CESTE MARLIS.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - DALLE CESTE MARLIS.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>32</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1879</v>
+        <v>1948</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1511</v>
+        <v>1575</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>564</v>
+        <v>599</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,28 +842,28 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>432</v>
+        <v>449</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>268</v>
+        <v>292</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="N11" s="12" t="n">
         <v>17</v>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="L12" s="12" t="n">
         <v>17</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>232</v>
+        <v>251</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>29</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>47</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>8</v>
@@ -1081,13 +1081,13 @@
         <v>111</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>5</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J15" s="12" t="n">
         <v>91</v>
@@ -1099,14 +1099,14 @@
         <v>21</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>39</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I16" s="12" t="n">
         <v>7</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>22</v>
@@ -1158,14 +1158,14 @@
         <v>22</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1196,52 +1196,52 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>13</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>17</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>03853</t>
+          <t>23971</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>VERONA</t>
+          <t>LONIGO</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>VIA FARINATA DEGLI UBERTI 16</t>
+          <t>VARIANTE SS 500 SNC</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1251,56 +1251,56 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>MARCONI ANDREA</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>23971</t>
+          <t>03853</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>LONIGO</t>
+          <t>VERONA</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>VARIANTE SS 500 SNC</t>
+          <t>VIA FARINATA DEGLI UBERTI 16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1310,39 +1310,39 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>MARCONI ANDREA</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1373,35 +1373,35 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L20" s="12" t="n">
         <v>7</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1432,28 +1432,28 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L21" s="12" t="n">
         <v>11</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>38</v>
@@ -1467,17 +1467,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>13911</t>
+          <t>05887</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>ALBETTONE</t>
+          <t>FERRARA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>VIA FORNACI 10    SS 247</t>
+          <t>VIA MODENA, 236/P</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1487,56 +1487,56 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>CARRARO COSA MIHAI EMILIAN</t>
+          <t>BASSI VALERIA</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05887</t>
+          <t>13911</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>FERRARA</t>
+          <t>ALBETTONE</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VIA MODENA, 236/P</t>
+          <t>VIA FORNACI 10    SS 247</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1546,39 +1546,39 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>BASSI VALERIA</t>
+          <t>CARRARO COSA MIHAI EMILIAN</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>0</v>
@@ -1621,7 +1621,7 @@
         <v>0</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>18</v>
@@ -1630,14 +1630,14 @@
         <v>11</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G25" s="12" t="n">
         <v>29</v>
@@ -1680,7 +1680,7 @@
         <v>4</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>15</v>
@@ -1689,7 +1689,7 @@
         <v>12</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>3</v>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L26" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1786,52 +1786,52 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>5</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>23964</t>
+          <t>03775</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>SAN VITO DI LEGUZZANO</t>
+          <t>SAN GIOVANNI LUPATOTO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VIA MARTIRI DELLA LIBERTA 43</t>
+          <t>VIA GAROFOLI N. 270</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,17 +1841,17 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>MARCONI ANDREA</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="I28" s="12" t="n">
         <v>0</v>
@@ -1860,37 +1860,37 @@
         <v>43</v>
       </c>
       <c r="K28" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="L28" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="M28" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="N28" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="L28" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M28" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="N28" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>03775</t>
+          <t>23964</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI LUPATOTO</t>
+          <t>SAN VITO DI LEGUZZANO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>VIA GAROFOLI N. 270</t>
+          <t>VIA MARTIRI DELLA LIBERTA 43</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1900,35 +1900,35 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>MARCONI ANDREA</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>2</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>1</v>
@@ -2022,31 +2022,31 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>3</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L31" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2102,14 +2102,14 @@
         <v>6</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
         <v>3</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>0</v>
@@ -2548,13 +2548,13 @@
         <v>0</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J40" s="12" t="n">
         <v>0</v>
@@ -2603,13 +2603,13 @@
         <v>0</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J41" s="12" t="n">
         <v>0</v>
@@ -2658,7 +2658,7 @@
         <v>0</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - DALLE CESTE MARLIS.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - DALLE CESTE MARLIS.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>32</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>1948</v>
+        <v>2065</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1575</v>
+        <v>1669</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>599</v>
+        <v>654</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>449</v>
+        <v>482</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>292</v>
+        <v>320</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,28 +901,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L12" s="12" t="n">
         <v>17</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>23</v>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>165</v>
+        <v>194</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>47</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>8</v>
@@ -1054,7 +1054,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>03994</t>
+          <t>03992</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>VIALE DELL'INDUSTRIA 140</t>
+          <t>VIA P.MARASCHIN 50</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1081,49 +1081,49 @@
         <v>111</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>03838</t>
+          <t>03994</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>VERONA</t>
+          <t>SCHIO</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>VIALE DEL LAVORO 22</t>
+          <t>VIALE DELL'INDUSTRIA 140</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1133,56 +1133,56 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>MARCONI ANDREA</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="I16" s="12" t="n">
         <v>7</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>246</v>
+        <v>158</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>03992</t>
+          <t>03838</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>SCHIO</t>
+          <t>VERONA</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>VIA P.MARASCHIN 50</t>
+          <t>VIALE DEL LAVORO 22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1192,35 +1192,35 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>MARCONI ANDREA</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>137</v>
+        <v>277</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1231,17 +1231,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>23971</t>
+          <t>03853</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>LONIGO</t>
+          <t>VERONA</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>VARIANTE SS 500 SNC</t>
+          <t>VIA FARINATA DEGLI UBERTI 16</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1251,56 +1251,56 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>MARCONI ANDREA</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>03853</t>
+          <t>23971</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>VERONA</t>
+          <t>LONIGO</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>VIA FARINATA DEGLI UBERTI 16</t>
+          <t>VARIANTE SS 500 SNC</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1310,39 +1310,39 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>MARCONI ANDREA</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
+        <v>87</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>162</v>
+      </c>
+      <c r="H19" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="I19" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="J19" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="K19" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="L19" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="M19" s="12" t="n">
+        <v>125</v>
+      </c>
+      <c r="N19" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="G19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="12" t="n">
-        <v>75</v>
-      </c>
-      <c r="I19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="12" t="n">
-        <v>75</v>
-      </c>
-      <c r="K19" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="L19" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="M19" s="12" t="n">
-        <v>94</v>
-      </c>
-      <c r="N19" s="12" t="n">
-        <v>50</v>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1373,31 +1373,31 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="I20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1432,52 +1432,52 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H21" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="I21" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="I21" s="12" t="n">
-        <v>20</v>
-      </c>
       <c r="J21" s="12" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L21" s="12" t="n">
         <v>11</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05887</t>
+          <t>13911</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>FERRARA</t>
+          <t>ALBETTONE</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>VIA MODENA, 236/P</t>
+          <t>VIA FORNACI 10    SS 247</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1487,56 +1487,56 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>BASSI VALERIA</t>
+          <t>CARRARO COSA MIHAI EMILIAN</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H22" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="I22" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="J22" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="K22" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="I22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="12" t="n">
-        <v>49</v>
-      </c>
-      <c r="K22" s="12" t="n">
-        <v>8</v>
-      </c>
       <c r="L22" s="12" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>13911</t>
+          <t>05887</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>ALBETTONE</t>
+          <t>FERRARA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VIA FORNACI 10    SS 247</t>
+          <t>VIA MODENA, 236/P</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1546,39 +1546,39 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>CARRARO COSA MIHAI EMILIAN</t>
+          <t>BASSI VALERIA</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>0</v>
@@ -1621,23 +1621,23 @@
         <v>0</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>18</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1668,28 +1668,28 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I25" s="12" t="n">
         <v>4</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L25" s="12" t="n">
         <v>12</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>3</v>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>8</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>0</v>
@@ -1798,16 +1798,16 @@
         <v>0</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>5</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="N27" s="12" t="n">
         <v>36</v>
@@ -1845,13 +1845,13 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I28" s="12" t="n">
         <v>0</v>
@@ -1863,17 +1863,17 @@
         <v>19</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1904,31 +1904,31 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L29" s="12" t="n">
         <v>2</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1963,13 +1963,13 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>0</v>
@@ -1981,17 +1981,17 @@
         <v>3</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2025,7 +2025,7 @@
         <v>26</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>2</v>
@@ -2043,10 +2043,10 @@
         <v>6</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>0</v>
@@ -2099,17 +2099,17 @@
         <v>7</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2140,22 +2140,22 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L33" s="12" t="n">
         <v>1</v>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
         <v>3</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>0</v>
@@ -2548,13 +2548,13 @@
         <v>0</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J40" s="12" t="n">
         <v>0</v>
@@ -2603,7 +2603,7 @@
         <v>0</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>0</v>
@@ -2658,7 +2658,7 @@
         <v>0</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - DALLE CESTE MARLIS.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - DALLE CESTE MARLIS.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>32</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2065</v>
+        <v>2173</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1669</v>
+        <v>1753</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>654</v>
+        <v>700</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>482</v>
+        <v>504</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>320</v>
+        <v>351</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>500</v>
+        <v>525</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I12" s="12" t="n">
         <v>41</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="L12" s="12" t="n">
         <v>17</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>194</v>
+        <v>230</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1019,28 +1019,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>8</v>
@@ -1054,17 +1054,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>03992</t>
+          <t>03838</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>SCHIO</t>
+          <t>VERONA</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>VIA P.MARASCHIN 50</t>
+          <t>VIALE DEL LAVORO 22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1074,35 +1074,35 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>MARCONI ANDREA</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>113</v>
+        <v>39</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>149</v>
+        <v>303</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>03994</t>
+          <t>03992</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>VIALE DELL'INDUSTRIA 140</t>
+          <t>VIA P.MARASCHIN 50</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1137,52 +1137,52 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>03838</t>
+          <t>03994</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>VERONA</t>
+          <t>SCHIO</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>VIALE DEL LAVORO 22</t>
+          <t>VIALE DELL'INDUSTRIA 140</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1192,35 +1192,35 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>MARCONI ANDREA</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>39</v>
+        <v>97</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>7</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>277</v>
+        <v>160</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1231,17 +1231,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>03853</t>
+          <t>03906</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>VERONA</t>
+          <t>ARZIGNANO</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>VIA FARINATA DEGLI UBERTI 16</t>
+          <t>VIA CHIAMPO 19</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1251,35 +1251,35 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>MARCONI ANDREA</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="I18" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="12" t="n">
         <v>78</v>
       </c>
-      <c r="I18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="12" t="n">
-        <v>79</v>
-      </c>
       <c r="K18" s="12" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,31 +1314,31 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1349,17 +1349,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>03906</t>
+          <t>03853</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ARZIGNANO</t>
+          <t>VERONA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VIA CHIAMPO 19</t>
+          <t>VIA FARINATA DEGLI UBERTI 16</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,39 +1369,39 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>MARCONI ANDREA</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
+        <v>91</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="12" t="n">
+        <v>79</v>
+      </c>
+      <c r="I20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="G20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="I20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="12" t="n">
-        <v>73</v>
-      </c>
       <c r="K20" s="12" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1432,10 +1432,10 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>27</v>
@@ -1444,7 +1444,7 @@
         <v>22</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>30</v>
@@ -1453,14 +1453,14 @@
         <v>11</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1491,19 +1491,19 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>19</v>
@@ -1512,7 +1512,7 @@
         <v>23</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>9</v>
@@ -1526,7 +1526,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05887</t>
+          <t>05829</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VIA MODENA, 236/P</t>
+          <t>VIA RAVENNA 78</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1550,42 +1550,42 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="12" t="n">
+        <v>63</v>
+      </c>
+      <c r="K23" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="I23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="12" t="n">
-        <v>50</v>
-      </c>
-      <c r="K23" s="12" t="n">
-        <v>9</v>
-      </c>
       <c r="L23" s="12" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>132</v>
+        <v>95</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>05829</t>
+          <t>05887</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VIA RAVENNA 78</t>
+          <t>VIA MODENA, 236/P</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1609,35 +1609,35 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>93</v>
+        <v>137</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1668,31 +1668,31 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I25" s="12" t="n">
         <v>4</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1703,17 +1703,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>03793</t>
+          <t>03775</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>BUSSOLENGO</t>
+          <t>SAN GIOVANNI LUPATOTO</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>VIA GARDESANA 25</t>
+          <t>VIA GAROFOLI N. 270</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1727,52 +1727,52 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>74</v>
+        <v>1</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>106</v>
+        <v>54</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>03827</t>
+          <t>03793</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>SAN BONIFACIO</t>
+          <t>BUSSOLENGO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>LOC. VILLABELLA N. 19 S.S. 11</t>
+          <t>VIA GARDESANA 25</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1782,35 +1782,35 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>MARCONI ANDREA</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1821,17 +1821,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>03775</t>
+          <t>03827</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI LUPATOTO</t>
+          <t>SAN BONIFACIO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VIA GAROFOLI N. 270</t>
+          <t>LOC. VILLABELLA N. 19 S.S. 11</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,35 +1841,35 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>MARCONI ANDREA</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1904,35 +1904,35 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L29" s="12" t="n">
         <v>2</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1978,20 +1978,20 @@
         <v>28</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L30" s="12" t="n">
         <v>3</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2025,10 +2025,10 @@
         <v>26</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>3</v>
@@ -2043,10 +2043,10 @@
         <v>6</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>0</v>
@@ -2096,20 +2096,20 @@
         <v>17</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
         <v>9</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" s="12" t="n">
         <v>3</v>
@@ -2279,10 +2279,10 @@
         <v>0</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         <v>3</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>0</v>
@@ -2548,13 +2548,13 @@
         <v>0</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J40" s="12" t="n">
         <v>0</v>
@@ -2603,7 +2603,7 @@
         <v>0</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>0</v>
@@ -2658,7 +2658,7 @@
         <v>0</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - DALLE CESTE MARLIS.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - DALLE CESTE MARLIS.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>32</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2173</v>
+        <v>2327</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1753</v>
+        <v>1870</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>700</v>
+        <v>762</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>504</v>
+        <v>528</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>351</v>
+        <v>392</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>81</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>525</v>
+        <v>550</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>197</v>
+        <v>236</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>160</v>
+        <v>191</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>230</v>
+        <v>284</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>52</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,35 +1078,35 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>303</v>
+        <v>335</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1137,35 +1137,35 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>118</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I16" s="12" t="n">
         <v>14</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1196,28 +1196,28 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>23</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>3</v>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="I18" s="12" t="n">
         <v>1</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M18" s="12" t="n">
+        <v>101</v>
+      </c>
+      <c r="N18" s="12" t="n">
         <v>85</v>
-      </c>
-      <c r="N18" s="12" t="n">
-        <v>72</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,31 +1314,31 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L19" s="12" t="n">
         <v>17</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1373,35 +1373,35 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="I20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L20" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1432,31 +1432,31 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>27</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1491,19 +1491,19 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>19</v>
@@ -1512,14 +1512,14 @@
         <v>23</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>0</v>
@@ -1562,16 +1562,16 @@
         <v>0</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L23" s="12" t="n">
         <v>13</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>0</v>
@@ -1609,16 +1609,16 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" s="12" t="n">
         <v>19</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" s="12" t="n">
         <v>50</v>
@@ -1627,34 +1627,34 @@
         <v>9</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>03817</t>
+          <t>03775</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>PESCHIERA DEL GARDA</t>
+          <t>SAN GIOVANNI LUPATOTO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>VIA VENEZIA 76</t>
+          <t>VIA GAROFOLI N. 270</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1668,52 +1668,52 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>123</v>
+        <v>63</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>03775</t>
+          <t>03817</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI LUPATOTO</t>
+          <t>PESCHIERA DEL GARDA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>VIA GAROFOLI N. 270</t>
+          <t>VIA VENEZIA 76</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1727,52 +1727,52 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="L26" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="M26" s="12" t="n">
+        <v>130</v>
+      </c>
+      <c r="N26" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="M26" s="12" t="n">
-        <v>54</v>
-      </c>
-      <c r="N26" s="12" t="n">
-        <v>22</v>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>03793</t>
+          <t>03827</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>BUSSOLENGO</t>
+          <t>SAN BONIFACIO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>VIA GARDESANA 25</t>
+          <t>LOC. VILLABELLA N. 19 S.S. 11</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1782,56 +1782,56 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>MARCONI ANDREA</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="K27" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="J27" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="K27" s="12" t="n">
-        <v>9</v>
-      </c>
       <c r="L27" s="12" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>03827</t>
+          <t>03793</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>SAN BONIFACIO</t>
+          <t>BUSSOLENGO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>LOC. VILLABELLA N. 19 S.S. 11</t>
+          <t>VIA GARDESANA 25</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,35 +1841,35 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>MARCONI ANDREA</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>0</v>
@@ -1922,13 +1922,13 @@
         <v>20</v>
       </c>
       <c r="L29" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M29" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="N29" s="12" t="n">
         <v>2</v>
-      </c>
-      <c r="M29" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="N29" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>0</v>
@@ -1975,7 +1975,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>4</v>
@@ -1984,14 +1984,14 @@
         <v>3</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2022,10 +2022,10 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>3</v>
@@ -2040,13 +2040,13 @@
         <v>9</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>9</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>0</v>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
         <v>9</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H34" s="12" t="n">
         <v>3</v>
@@ -2258,7 +2258,7 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>0</v>
@@ -2270,10 +2270,10 @@
         <v>0</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L35" s="12" t="n">
         <v>0</v>
@@ -2379,7 +2379,7 @@
         <v>3</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>0</v>
@@ -2548,13 +2548,13 @@
         <v>0</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J40" s="12" t="n">
         <v>0</v>
@@ -2603,7 +2603,7 @@
         <v>0</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>0</v>
@@ -2658,7 +2658,7 @@
         <v>0</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/RZV - DALLE CESTE MARLIS.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - DALLE CESTE MARLIS.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O42" headerRowCount="1">
-  <autoFilter ref="A10:O42"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O39" headerRowCount="1">
+  <autoFilter ref="A10:O39"/>
   <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:O39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -681,16 +681,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2327</v>
+        <v>2118</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1870</v>
+        <v>1719</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>762</v>
+        <v>653</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -818,17 +818,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>05820</t>
+          <t>13948</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>FERRARA</t>
+          <t>CORNEDO VICENTINO</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>VIA BOLOGNA 632</t>
+          <t>VIA MONTE ORTIGARA 24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -838,35 +838,35 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>BASSI VALERIA</t>
+          <t>MARCONI ANDREA</t>
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>292</v>
+        <v>237</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>528</v>
+        <v>397</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>122</v>
+        <v>44</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>392</v>
+        <v>42</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>81</v>
+        <v>19</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>550</v>
+        <v>284</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -877,17 +877,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>13948</t>
+          <t>03979</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>CORNEDO VICENTINO</t>
+          <t>VICENZA</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>VIA MONTE ORTIGARA 24</t>
+          <t>VIA TRIESTE</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -897,56 +897,56 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>MARCONI ANDREA</t>
+          <t>CARRARO COSA MIHAI EMILIAN</t>
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>397</v>
+        <v>229</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>44</v>
+        <v>124</v>
       </c>
       <c r="I12" s="12" t="n">
+        <v>115</v>
+      </c>
+      <c r="J12" s="12" t="n">
+        <v>191</v>
+      </c>
+      <c r="K12" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="L12" s="12" t="n">
         <v>42</v>
-      </c>
-      <c r="J12" s="12" t="n">
-        <v>210</v>
-      </c>
-      <c r="K12" s="12" t="n">
-        <v>85</v>
-      </c>
-      <c r="L12" s="12" t="n">
-        <v>19</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>284</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>25</v>
+        <v>154</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>03979</t>
+          <t>03355</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>VICENZA</t>
+          <t>ROVIGO</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>VIA TRIESTE</t>
+          <t>VIALE PORTA PO 66/B</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -956,39 +956,39 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>CARRARO COSA MIHAI EMILIAN</t>
+          <t>MARTELLATO MARCO</t>
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>229</v>
+        <v>382</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>124</v>
+        <v>33</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>115</v>
+        <v>21</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>284</v>
+        <v>506</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>154</v>
+        <v>5</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>BASSI VALERIA</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>BASSI VALERIA</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>BASSI VALERIA</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
@@ -1526,17 +1526,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05829</t>
+          <t>03775</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>FERRARA</t>
+          <t>SAN GIOVANNI LUPATOTO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VIA RAVENNA 78</t>
+          <t>VIA GAROFOLI N. 270</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1550,31 +1550,31 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="I23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>101</v>
+        <v>63</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1585,17 +1585,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>05887</t>
+          <t>03817</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>FERRARA</t>
+          <t>PESCHIERA DEL GARDA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VIA MODENA, 236/P</t>
+          <t>VIA VENEZIA 76</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1609,52 +1609,52 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>03775</t>
+          <t>03827</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI LUPATOTO</t>
+          <t>SAN BONIFACIO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>VIA GAROFOLI N. 270</t>
+          <t>LOC. VILLABELLA N. 19 S.S. 11</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1664,56 +1664,56 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>MARCONI ANDREA</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="I25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>63</v>
+        <v>96</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>03817</t>
+          <t>03793</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>PESCHIERA DEL GARDA</t>
+          <t>BUSSOLENGO</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>VIA VENEZIA 76</t>
+          <t>VIA GARDESANA 25</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1723,35 +1723,35 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>BASSI VALERIA</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1762,17 +1762,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>03827</t>
+          <t>23964</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>SAN BONIFACIO</t>
+          <t>SAN VITO DI LEGUZZANO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>LOC. VILLABELLA N. 19 S.S. 11</t>
+          <t>VIA MARTIRI DELLA LIBERTA 43</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1786,52 +1786,52 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>20</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>96</v>
+        <v>26</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>03793</t>
+          <t>03965</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>BUSSOLENGO</t>
+          <t>THIENE</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VIA GARDESANA 25</t>
+          <t>VIA MARCONI 123/A</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,56 +1841,56 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>CARRARO COSA MIHAI EMILIAN</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>117</v>
+        <v>48</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>23964</t>
+          <t>13850</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>SAN VITO DI LEGUZZANO</t>
+          <t>ZEVIO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>VIA MARTIRI DELLA LIBERTA 43</t>
+          <t>S.S.434 TRANSPOLESANA KM.7+400</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1900,56 +1900,56 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>MARCONI ANDREA</t>
+          <t>BASSI VALERIA</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>03965</t>
+          <t>51516</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>THIENE</t>
+          <t>VILLAFRANCA DI VERONA</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>VIA MARCONI 123/A</t>
+          <t>VIA POSTUMIA N.  86</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1959,56 +1959,56 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>CARRARO COSA MIHAI EMILIAN</t>
+          <t>BASSI VALERIA</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="K30" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L30" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I30" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="K30" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="L30" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="M30" s="12" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>13850</t>
+          <t>03961</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>ZEVIO</t>
+          <t>VICENZA</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>S.S.434 TRANSPOLESANA KM.7+400</t>
+          <t>VIALE SAN LAZZARO 106</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2018,56 +2018,56 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>BASSI VALERIA</t>
+          <t>CARRARO COSA MIHAI EMILIAN</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>94</v>
+        <v>2</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>51516</t>
+          <t>03826</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>VILLAFRANCA DI VERONA</t>
+          <t>VERONA</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>VIA POSTUMIA N.  86</t>
+          <t>VIA CAMPAGNOL DI TOMBETTA 6</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2077,56 +2077,56 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>BASSI VALERIA</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L32" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="M32" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="M32" s="12" t="n">
-        <v>39</v>
-      </c>
       <c r="N32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>03961</t>
+          <t>23973</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>VICENZA</t>
+          <t>MUSSOLENTE</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>VIALE SAN LAZZARO 106</t>
+          <t>VIA DANTE ALIGHIERI 47</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2140,31 +2140,31 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="M33" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="N33" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2175,17 +2175,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>03826</t>
+          <t>03993</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>VERONA</t>
+          <t>VICENZA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIA CAMPAGNOL DI TOMBETTA 6</t>
+          <t>VIA J. DAL VERME 188 189</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2195,32 +2195,32 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>CARRARO COSA MIHAI EMILIAN</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H34" s="12" t="n">
+      <c r="K34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="12" t="n">
         <v>3</v>
-      </c>
-      <c r="I34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="K34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="M34" s="12" t="n">
-        <v>9</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>0</v>
@@ -2234,17 +2234,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>23973</t>
+          <t>13834</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>MUSSOLENTE</t>
+          <t>ISOLA RIZZA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>VIA DANTE ALIGHIERI 47</t>
+          <t>VIA MUSELLE S.S.434 KM 22+224</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2254,73 +2254,69 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>CARRARO COSA MIHAI EMILIAN</t>
+          <t>MARTELLATO MARCO</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>03993</t>
+          <t>03816</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>VICENZA</t>
+          <t>SONA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>VIA J. DAL VERME 188 189</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
+          <t>LOCALITA' CIVEL 1</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>CARRARO COSA MIHAI EMILIAN</t>
+          <t>BASSI VALERIA</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H36" s="12" t="n">
         <v>0</v>
@@ -2329,7 +2325,7 @@
         <v>0</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>0</v>
@@ -2338,7 +2334,7 @@
         <v>0</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>0</v>
@@ -2352,17 +2348,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>13834</t>
+          <t>13862</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>ISOLA RIZZA</t>
+          <t>VALEGGIO SUL MINCIO</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>VIA MUSELLE S.S.434 KM 22+224</t>
+          <t>VIA VILLAFRANCA 357</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2376,28 +2372,28 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="12" t="n">
         <v>2</v>
-      </c>
-      <c r="J37" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M37" s="12" t="n">
-        <v>20</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>0</v>
@@ -2411,37 +2407,37 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>03816</t>
+          <t>57208</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>SONA</t>
+          <t>VERONA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>LOCALITA' CIVEL 1</t>
+          <t>VIA MANTOVANA 90</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>BASSI VALERIA</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="12" t="n">
+        <v>147</v>
+      </c>
+      <c r="H38" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H38" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J38" s="12" t="n">
         <v>0</v>
       </c>
@@ -2459,24 +2455,24 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>05861</t>
+          <t>55905</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>COPPARO</t>
+          <t>VILLAFRANCA DI VERONA</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VIA PRIMICELLO 26</t>
+          <t>VIA SAN GIOVANI PAGLIA 23</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr"/>
@@ -2489,13 +2485,13 @@
         <v>0</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="H39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" s="12" t="n">
         <v>0</v>
@@ -2513,175 +2509,6 @@
         <v>0</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>Bene</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>13862</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>VALEGGIO SUL MINCIO</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>VIA VILLAFRANCA 357</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Fabio Villa</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="H40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="J40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="N40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>57208</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>VERONA</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>VIA MANTOVANA 90</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr"/>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="12" t="n">
-        <v>147</v>
-      </c>
-      <c r="H41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="J41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>55905</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>VILLAFRANCA DI VERONA</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>VIA SAN GIOVANI PAGLIA 23</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr"/>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="F42" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="H42" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>

--- a/docs/files/REPORT_FILTRI/RZV - DALLE CESTE MARLIS.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - DALLE CESTE MARLIS.xlsx
@@ -684,13 +684,13 @@
         <v>29</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2118</v>
+        <v>2109</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>1719</v>
+        <v>0</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>653</v>
+        <v>645</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -818,17 +818,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>13948</t>
+          <t>03979</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>CORNEDO VICENTINO</t>
+          <t>VICENZA</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>VIA MONTE ORTIGARA 24</t>
+          <t>VIA TRIESTE</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -838,56 +838,56 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>MARCONI ANDREA</t>
+          <t>CARRARO COSA MIHAI EMILIAN</t>
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>397</v>
+        <v>222</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="I11" s="12" t="n">
+        <v>109</v>
+      </c>
+      <c r="J11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="L11" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="J11" s="12" t="n">
-        <v>210</v>
-      </c>
-      <c r="K11" s="12" t="n">
-        <v>85</v>
-      </c>
-      <c r="L11" s="12" t="n">
-        <v>19</v>
-      </c>
       <c r="M11" s="12" t="n">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>25</v>
+        <v>146</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>03979</t>
+          <t>03355</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>VICENZA</t>
+          <t>ROVIGO</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>VIA TRIESTE</t>
+          <t>VIALE PORTA PO 66/B</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -897,56 +897,56 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>CARRARO COSA MIHAI EMILIAN</t>
+          <t>MARTELLATO MARCO</t>
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>229</v>
+        <v>381</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>124</v>
+        <v>33</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>115</v>
+        <v>20</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>284</v>
+        <v>501</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>154</v>
+        <v>5</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>03355</t>
+          <t>13948</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>ROVIGO</t>
+          <t>CORNEDO VICENTINO</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>VIALE PORTA PO 66/B</t>
+          <t>VIA MONTE ORTIGARA 24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -956,35 +956,35 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>MARTELLATO MARCO</t>
+          <t>MARCONI ANDREA</t>
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>506</v>
+        <v>278</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1025,13 +1025,13 @@
         <v>262</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>87</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>33</v>
@@ -1040,7 +1040,7 @@
         <v>52</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>9</v>
@@ -1078,19 +1078,19 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>35</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>29</v>
@@ -1099,14 +1099,14 @@
         <v>30</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>30</v>
@@ -1149,7 +1149,7 @@
         <v>14</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>39</v>
@@ -1158,14 +1158,14 @@
         <v>21</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>6</v>
@@ -1208,7 +1208,7 @@
         <v>8</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>23</v>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1267,7 +1267,7 @@
         <v>1</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>43</v>
@@ -1317,16 +1317,16 @@
         <v>98</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>28</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>33</v>
@@ -1335,10 +1335,10 @@
         <v>17</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>0</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>44</v>
@@ -1432,10 +1432,10 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>27</v>
@@ -1444,7 +1444,7 @@
         <v>26</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>31</v>
@@ -1453,10 +1453,10 @@
         <v>17</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1491,19 +1491,19 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>20</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>19</v>
@@ -1512,7 +1512,7 @@
         <v>23</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>10</v>
@@ -1526,17 +1526,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>03775</t>
+          <t>03817</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI LUPATOTO</t>
+          <t>PESCHIERA DEL GARDA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VIA GAROFOLI N. 270</t>
+          <t>VIA VENEZIA 76</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1553,28 +1553,28 @@
         <v>64</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="L23" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="M23" s="12" t="n">
+        <v>125</v>
+      </c>
+      <c r="N23" s="12" t="n">
         <v>6</v>
-      </c>
-      <c r="M23" s="12" t="n">
-        <v>63</v>
-      </c>
-      <c r="N23" s="12" t="n">
-        <v>24</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1585,17 +1585,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>03817</t>
+          <t>03775</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>PESCHIERA DEL GARDA</t>
+          <t>SAN GIOVANNI LUPATOTO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VIA VENEZIA 76</t>
+          <t>VIA GAROFOLI N. 270</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1612,32 +1612,32 @@
         <v>62</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>130</v>
+        <v>62</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G25" s="12" t="n">
         <v>0</v>
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>20</v>
@@ -1689,7 +1689,7 @@
         <v>8</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>37</v>
@@ -1727,19 +1727,19 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>18</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>9</v>
@@ -1748,14 +1748,14 @@
         <v>14</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>10</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>0</v>
@@ -1798,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>20</v>
@@ -1857,7 +1857,7 @@
         <v>0</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>4</v>
@@ -1904,10 +1904,10 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>3</v>
@@ -1916,7 +1916,7 @@
         <v>3</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>9</v>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>0</v>
@@ -1975,7 +1975,7 @@
         <v>0</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>8</v>
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>0</v>
@@ -2034,7 +2034,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>2</v>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>3</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2152,7 @@
         <v>0</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>4</v>
@@ -2211,7 +2211,7 @@
         <v>0</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K34" s="12" t="n">
         <v>0</v>
@@ -2220,14 +2220,14 @@
         <v>0</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2261,16 +2261,16 @@
         <v>3</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="H35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K35" s="12" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2375,7 +2375,7 @@
         <v>0</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>0</v>
@@ -2430,7 +2430,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H38" s="12" t="n">
         <v>0</v>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
